--- a/data/exercise1.xlsx
+++ b/data/exercise1.xlsx
@@ -1,26 +1,1626 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schneids\code\building-archetype-inference\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9221EE84-2892-44EF-9538-C4A74EB1C3FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="11388" yWindow="-17388" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="525">
+  <si>
+    <t>Geometry</t>
+  </si>
+  <si>
+    <t>Building Period</t>
+  </si>
+  <si>
+    <t>Building Quality</t>
+  </si>
+  <si>
+    <t>thermisch wirksame Speichermasse</t>
+  </si>
+  <si>
+    <t>Energie-versorgung</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Projektname_</t>
+  </si>
+  <si>
+    <t>Adresse_</t>
+  </si>
+  <si>
+    <t>Erstellungsdatum_</t>
+  </si>
+  <si>
+    <t>Variante / Scenario_</t>
+  </si>
+  <si>
+    <t>GFZ_</t>
+  </si>
+  <si>
+    <t>Sanierungsanteil_</t>
+  </si>
+  <si>
+    <t>Raumhöhe _m Netto</t>
+  </si>
+  <si>
+    <t>Charakteristische Länge (lc)_m</t>
+  </si>
+  <si>
+    <t>Wetterdatensatz Name_</t>
+  </si>
+  <si>
+    <t>Wetterdatensatz Nummer_</t>
+  </si>
+  <si>
+    <t>Außentemperatur Jahresmittel_°C</t>
+  </si>
+  <si>
+    <t>Mittelaußentemperatur Heizperiode_°C</t>
+  </si>
+  <si>
+    <t>Mittelaußentemperatur Kühlperiode_°C</t>
+  </si>
+  <si>
+    <t>Nutzungsmischung_</t>
+  </si>
+  <si>
+    <t>Nutzerstrom_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Beleuchtung_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Allgemeinstrom_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Heiwärmebedarf_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Külenergiebedarf_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>WWWB_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Lüftungsenergiebedarf_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>E-Mobilität_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Fossile Mobilität_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Spalte3_</t>
+  </si>
+  <si>
+    <t>Transmissionswärmeverl._kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Lüftungswärmeverluste_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Nachtlüftung_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Solare Gewinne_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Innere Wärmen_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Heizwärmebedarf_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Kühlbedarf (KB)_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>ML Wärmerückgewinnung_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Wärmebilanz_WAHR</t>
+  </si>
+  <si>
+    <t>Transmissionswärmeverl.4_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Lüftungswärmeverluste5_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Nachtlüftung6_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Solare Gewinne7_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Innere Wärmen8_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Heizwärmebedarf9_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Kühlbedarf (KB)10_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Wärmebilanz Heizperiode_FALSCH</t>
+  </si>
+  <si>
+    <t>Transmission AW_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Transmission Dach_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Transmission KD/EFB_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Transmission Fenster_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Transmission Wärmebrücken_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Infiltration_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Lüftung Fenster_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Mechanische Lüftung_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>ML Wärmerückgewinnung11_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Heizwärmebedarf Statisch_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Heizwärmebedarf Flexibel_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Kühlbedarf Statisch_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Kühlbedarf Flexibel_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Anteil Flexibler Heizung an Gesamtheizung_</t>
+  </si>
+  <si>
+    <t>Anteil Flexibler Kühlung an Gesamtkühlung_</t>
+  </si>
+  <si>
+    <t>Transmissionswärmeverl.12_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Lüftungswärmeverluste13_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Nachtlüftung gekühlt_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Solare Gewinne14_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Innere Wärmen15_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Heizwärmebedarf16_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Kühlbedarf (KB)17_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Wärmebilanz Kühlperiode_FALSCH</t>
+  </si>
+  <si>
+    <t>Transmission AW18_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Transmission Dach19_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Transmission KD/EFB20_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Transmission Fenster21_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Transmission Wärmebrücken22_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Infiltration23_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Lüftung Fenster24_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Mechanische Lüftung25_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>ML Wärmerückgewinnung 2_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Heizwärmebedarf Statisch26_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Heizwärmebedarf Flexibel27_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Kühlbedarf Statisch28_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Kühlbedarf Flexibel29_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Anteil Flexibler Heizung an Gesamtheizung30_</t>
+  </si>
+  <si>
+    <t>Anteil Flexibler Kühlung an Gesamtkühlung31_</t>
+  </si>
+  <si>
+    <t>Wärmebilanz32_WAHR</t>
+  </si>
+  <si>
+    <t>Transmissionswärmeverl.33_kWh/m²NGFungekühlta</t>
+  </si>
+  <si>
+    <t>Lüftungswärmeverluste34_kWh/m²NGFungekühlta</t>
+  </si>
+  <si>
+    <t>Nachtlüftung35_kWh/m²NGFungekühlta</t>
+  </si>
+  <si>
+    <t>Solare Gewinne36_kWh/m²NGFungekühlta</t>
+  </si>
+  <si>
+    <t>Innere Wärmen37_kWh/m²NGFungekühlta</t>
+  </si>
+  <si>
+    <t>Heizwärmebedarf38_kWh/m²NGFungekühlta</t>
+  </si>
+  <si>
+    <t>Transmission AW39_kWh/m²NGFungekühlta</t>
+  </si>
+  <si>
+    <t>Transmission Dach40_kWh/m²NGFungekühlta</t>
+  </si>
+  <si>
+    <t>Transmission KD/EFB41_kWh/m²NGFungekühlta</t>
+  </si>
+  <si>
+    <t>Transmission Fenster42_kWh/m²NGFungekühlta</t>
+  </si>
+  <si>
+    <t>Transmission Wärmebrücken43_kWh/m²NGFungekühlta</t>
+  </si>
+  <si>
+    <t>Infiltration44_kWh/m²NGFungekühlta</t>
+  </si>
+  <si>
+    <t>Lüftung Fenster45_kWh/m²NGFungekühlta</t>
+  </si>
+  <si>
+    <t>Mechanische Lüftung46_kWh/m²NGFungekühlta</t>
+  </si>
+  <si>
+    <t>ML Wärmerückgewinnung47_kWh/m²NGFungekühlta</t>
+  </si>
+  <si>
+    <t>Heizwärmebedarf Statisch48_kWh/m²NGFungekühlta</t>
+  </si>
+  <si>
+    <t>Heizwärmebedarf Flexibel49_kWh/m²NGFungekühlta</t>
+  </si>
+  <si>
+    <t>Flexibilitätsanteil_%</t>
+  </si>
+  <si>
+    <t>Transmissionswärmeverl.50_kWh/m²NGFgekühlta</t>
+  </si>
+  <si>
+    <t>Lüftungswärmeverluste51_kWh/m²NGFgekühlta</t>
+  </si>
+  <si>
+    <t>Nachtlüftung gekühlt52_kWh/m²NGFgekühlta</t>
+  </si>
+  <si>
+    <t>Solare Gewinne53_kWh/m²NGFgekühlta</t>
+  </si>
+  <si>
+    <t>Innere Wärmen54_kWh/m²NGFgekühlta</t>
+  </si>
+  <si>
+    <t>Heizwärmebedarf55_kWh/m²NGFgekühlta</t>
+  </si>
+  <si>
+    <t>Kühlbedarf (KB)56_kWh/m²NGFgekühlta</t>
+  </si>
+  <si>
+    <t>Transmission AW57_kWh/m²NGFgekühlta</t>
+  </si>
+  <si>
+    <t>Transmission Dach58_kWh/m²NGFgekühlta</t>
+  </si>
+  <si>
+    <t>Transmission KD/EFB59_kWh/m²NGFgekühlta</t>
+  </si>
+  <si>
+    <t>Transmission Fenster60_kWh/m²NGFgekühlta</t>
+  </si>
+  <si>
+    <t>Transmission Wärmebrücken61_kWh/m²NGFgekühlta</t>
+  </si>
+  <si>
+    <t>Infiltration62_kWh/m²NGFgekühlta</t>
+  </si>
+  <si>
+    <t>Lüftung Fenster63_kWh/m²NGFgekühlta</t>
+  </si>
+  <si>
+    <t>Mechanische Lüftung64_kWh/m²NGFgekühlta</t>
+  </si>
+  <si>
+    <t>ML Wärmerückgewinnung65_kWh/m²NGFgekühlta</t>
+  </si>
+  <si>
+    <t>Heizwärmebedarf Statisch66_kWh/m²NGFgekühlta</t>
+  </si>
+  <si>
+    <t>Heizwärmebedarf Flexibel67_kWh/m²NGFgekühlta</t>
+  </si>
+  <si>
+    <t>Kühlbedarf Statisch68_kWh/m²NGFgekühlta</t>
+  </si>
+  <si>
+    <t>Kühlbedarf Flexibel69_kWh/m²NGFgekühlta</t>
+  </si>
+  <si>
+    <t>Flexibilitätsanteil70_</t>
+  </si>
+  <si>
+    <t>Flexibilitätsanteil71_</t>
+  </si>
+  <si>
+    <t>Flexibilitätsanteil72_</t>
+  </si>
+  <si>
+    <t>Mitteltemperatur ungekühlt_°C</t>
+  </si>
+  <si>
+    <t>Mitteltemperatur gekühlt_°C</t>
+  </si>
+  <si>
+    <t>Mitteltemperatur ungekühlt72_°C</t>
+  </si>
+  <si>
+    <t>Mitteltemperatur gekühlt73_°C</t>
+  </si>
+  <si>
+    <t>Mittlere Temperaturüberschreitung ungekühlt_K</t>
+  </si>
+  <si>
+    <t>Mittlere Temperaturüberschreitung gekühlt_K</t>
+  </si>
+  <si>
+    <t>Mittlere Temperaturunterschreitung ungekühlt_°C</t>
+  </si>
+  <si>
+    <t>Mittlere Temperaturunterschreitung gekühlt_°C</t>
+  </si>
+  <si>
+    <t>Spalte74_</t>
+  </si>
+  <si>
+    <t>Spalte75_</t>
+  </si>
+  <si>
+    <t>Nutzerstrom, Beleuchtung und Allgemeinstrom_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Nutzerstrom75_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Beleuchtung76_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Allgemeinstrom77_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Nutzerstrom Bilanz_WAHR</t>
+  </si>
+  <si>
+    <t>Heizen_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Heizen Hilfsstrom_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Spalte78_</t>
+  </si>
+  <si>
+    <t>Kühlen_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Heizen Hilfsstrom79_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Heizen Hilfsstrom80_</t>
+  </si>
+  <si>
+    <t>Warmwasser_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Lüftung_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>WW
+E-Stab_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>e-Speicher Beladung_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>EV Quartiersladung_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Quartier_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>PV Ertrag_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>PV Direktdeckung Haushaltsstrom_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>PV Direktdeckung Heizen_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>PV Direktdeckung Kühlen_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>PV Direktdeckung Warmwasser_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>PV Direktdeckung Lüftung_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>PV Direktdeckung MIV_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>PV Direktdeckung Quartier_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>PV Überdeckung Heizen_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>PV Überdeckung Kühlen_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>PV Überdeckung Warmwasser_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>PV Überdeckung WW
+E-Stab_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>PV Überdeckung e-Speicher Beladung_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>PV Überdeckung MIV_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>PV Überdeckung Quartier_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>PV Netzeinspeisung_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>E-Batterie → Nutzerstrom_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>E-Batterie → HKLS_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>E-Batterie_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>E-Batterie80_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>E-Batterie81_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>E-Batterie82_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>E-Batterie83_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>E-Batterie Verluste_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>E-Batterie84_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Flexible Direktdeckung → Nutzerstrom_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Flexible Direktdeckung → Heizen_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Flexible Direktdeckung → Kühlen_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Flexible Direktdeckung_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Flexible Direktdeckung85_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Flexible Direktdeckung86_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Flexible Direktdeckung87_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Flexible Direktdeckung vollständig_WAHR</t>
+  </si>
+  <si>
+    <t>Flexible Überdeckung → Heizen_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Flexible Überdeckung → Kühlen_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Flexible Überdeckung_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Flexible Überdeckung → Batterie_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Flexible Überdeckung88_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Flexible Überdeckung89_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Flexible Überdeckung vollständig_WAHR</t>
+  </si>
+  <si>
+    <t>Flexible Deckung → Gebäude_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Flexible Deckung Gebäude + MIV = Quartier_WAHR</t>
+  </si>
+  <si>
+    <t>E-Car Entladung → Nutzerstrom_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>E-Car Entladung → HKLS_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>E-Car Entladung_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>E-Car Entladung90_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>E-Car Entladung91_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>E-Car Entladung92_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>E-Car Entladung93_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>E-Car Entladung94_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Netzstrom → Nutzerstrom_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Netzstrom_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Netzstrom95_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Netzstrom96_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Netzstrom97_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Netzstrom → Gebäude_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Netzstrom98_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Netzstrom → Quartier_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Netzstrombilanz Gebäude + MIV = Insgesamt_WAHR</t>
+  </si>
+  <si>
+    <t>Netzstrombilanz_WAHR</t>
+  </si>
+  <si>
+    <t>E-Car Ladung Außerhalb des Quartiers_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Fernwärme_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Fernwärme99_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Fernwärme100_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Gas_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Gas101_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Gas102_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Biomasse_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Biomasse103_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Biomasse104_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Sonstige_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Sonstige105_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Sonstige106_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Sonstige107_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>MIV Fossil_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Abwärme_</t>
+  </si>
+  <si>
+    <t>Heizen 2_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Heizen 4_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Kühlen 2_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>WWWB1_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>WWWB2_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>WWWB3_</t>
+  </si>
+  <si>
+    <t>Netzstrom insg. (Flexibel und Inflexibel)_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>EV Beladung im Quartier_kWhPEges./m²NGFa</t>
+  </si>
+  <si>
+    <t>EV Beladung Netzäquivalent_kWhPEges./m²NGFa</t>
+  </si>
+  <si>
+    <t>EV Beladung Netzsubstitution_kWhPEges./m²NGFa</t>
+  </si>
+  <si>
+    <t>EV Own Travels_</t>
+  </si>
+  <si>
+    <t>Spalte108_</t>
+  </si>
+  <si>
+    <t>Kontextfaktor bauliche Dichte_kWhPEges./m²NGFa</t>
+  </si>
+  <si>
+    <t>Kontextfaktor Mobilität_kWhPEges./m²NGFa</t>
+  </si>
+  <si>
+    <t>Kontextfaktor Sanierung_kWhPEges./m²NGFa</t>
+  </si>
+  <si>
+    <t>Spalte109_</t>
+  </si>
+  <si>
+    <t>Betriebsenergie_kWhPEges./m²NGFa</t>
+  </si>
+  <si>
+    <t>Nutzerstrom110_kWhPEges./m²NGFa</t>
+  </si>
+  <si>
+    <t>HKLS Strom_kWhPEges./m²NGFa</t>
+  </si>
+  <si>
+    <t>HKLS Fernwärme_kWhPEges./m²NGFa</t>
+  </si>
+  <si>
+    <t>HKLS Erdgas_kWhPEges./m²NGFa</t>
+  </si>
+  <si>
+    <t>HKLS Biomasse_kWhPEges./m²NGFa</t>
+  </si>
+  <si>
+    <t>HKLS Sonstige_kWhPEges./m²NGFa</t>
+  </si>
+  <si>
+    <t>Mobilität (MIV)_kWhPEges./m²NGFa</t>
+  </si>
+  <si>
+    <t>MIV Fossil111_kWhPEges./m²NGFa</t>
+  </si>
+  <si>
+    <t>MIV Elektrisch_kWhPEges./m²NGFa</t>
+  </si>
+  <si>
+    <t>Speicher-Verluste_kWhPEges./m²NGFa</t>
+  </si>
+  <si>
+    <t>Spalte112_</t>
+  </si>
+  <si>
+    <t>Kontext bauliche Dichte_kWhPEges./m²NGFa</t>
+  </si>
+  <si>
+    <t>Kontext Mobilität_kWhPEges./m²NGFa</t>
+  </si>
+  <si>
+    <t>Kontext Sanierung_kWhPEges./m²NGFa</t>
+  </si>
+  <si>
+    <t>Lokale Erneuerbare (Netzstrom Substitutionsäquivalent)_kWhPEges./m²NGFa</t>
+  </si>
+  <si>
+    <t>Energieflexibilität (Netzstrom Substitutionsäquivalent)_kWhPEges./m²NGFa</t>
+  </si>
+  <si>
+    <t>PE-Bilanz Netzäquivalent_kWhPEges./m²NGFa</t>
+  </si>
+  <si>
+    <t>Spalte113_</t>
+  </si>
+  <si>
+    <t>Netzbezug_kWhPEges./m²NGFa</t>
+  </si>
+  <si>
+    <t>Flexibler Bezug_kWhPEges./m²NGFa</t>
+  </si>
+  <si>
+    <t>EV Externe Beladung_kWhPEges./m²NGFa</t>
+  </si>
+  <si>
+    <t>Primärenergie-Import_kWhPEges./m²NGFa</t>
+  </si>
+  <si>
+    <t>PV Netzeinspeisung PE_kWhPEges./m²NGFa</t>
+  </si>
+  <si>
+    <t>EV Other Travels _</t>
+  </si>
+  <si>
+    <t>Primärenergie-Export_kWhPEges./m²NGFa</t>
+  </si>
+  <si>
+    <t>PE-IE-Bilanz Projektwert_kWhPEges./m²NGFa</t>
+  </si>
+  <si>
+    <t>PE-IE-Bilanz Zielwert_kWhPEges./m²NGFa</t>
+  </si>
+  <si>
+    <t>importExport Saldo Projektwert - Zielwert_kWhPEges./m²NGFa</t>
+  </si>
+  <si>
+    <t>PE-Bilanz Virtuell = Import/Export_FALSCH</t>
+  </si>
+  <si>
+    <t>PE Faktor Netzstrom Statistisch_</t>
+  </si>
+  <si>
+    <t>PE Faktor Netzstrom Effektiv_</t>
+  </si>
+  <si>
+    <t>Spalte114_</t>
+  </si>
+  <si>
+    <t>Spalte115_</t>
+  </si>
+  <si>
+    <t>Spalte116_</t>
+  </si>
+  <si>
+    <t>Spalte117_</t>
+  </si>
+  <si>
+    <t>Bauteil Außenwand fossil_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>Bauteil Außenwand biogen_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>Bauteil Außenwand Lebensdauer_Jahre</t>
+  </si>
+  <si>
+    <t>Spalte118_</t>
+  </si>
+  <si>
+    <t>Spalte119_</t>
+  </si>
+  <si>
+    <t>Bauteil Außenwand_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>Bauteil Fenster fossil_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>Bauteil Fenster biogen_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>Bauteil Fenster Lebensdauer_Jahre</t>
+  </si>
+  <si>
+    <t>Spalte120_</t>
+  </si>
+  <si>
+    <t>Spalte121_</t>
+  </si>
+  <si>
+    <t>Bauteil Fenster _GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>Bauteil Dach fossil_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>Bauteil Dach biogen_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>Bauteil Dach Lebensdauer_Jahre</t>
+  </si>
+  <si>
+    <t>Spalte122_</t>
+  </si>
+  <si>
+    <t>Spalte123_</t>
+  </si>
+  <si>
+    <t>Bauteil Dach_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>Bauteil Decke gegen Erdreich / Keller fossil_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>Bauteil Decke gegen Erdreich / Keller biogen_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>Bauteil Decke gegen Erdreich / Keller Lebensdauer_Jahre</t>
+  </si>
+  <si>
+    <t>Spalte124_</t>
+  </si>
+  <si>
+    <t>Spalte125_</t>
+  </si>
+  <si>
+    <t>Bauteil Decke gegen Erdreich / Keller_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>Bauteil Zwischengeschoßdecken fossil_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>Bauteil Zwischengeschoßdecken biogen_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>Bauteil Zwischengeschoßdecken Lebensdauer_Jahre</t>
+  </si>
+  <si>
+    <t>Spalte126_</t>
+  </si>
+  <si>
+    <t>Spalte127_</t>
+  </si>
+  <si>
+    <t>Bauteil Zwischengeschoßdecken_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>Baulich Allgemein fossil_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>Baulich Allgemein biogen_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>Baulich Allgemein Lebensdauer_Jahre</t>
+  </si>
+  <si>
+    <t>Spalte128_</t>
+  </si>
+  <si>
+    <t>Spalte129_</t>
+  </si>
+  <si>
+    <t>Baulich Allgemein_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>Baulich Andere fossil_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>Baulich Andere biogen_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>Baulich Andere Lebensdauer_Jahre</t>
+  </si>
+  <si>
+    <t>Spalte130_</t>
+  </si>
+  <si>
+    <t>Spalte131_</t>
+  </si>
+  <si>
+    <t>Baulich Sammel-Maßnahmen_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>Baulich Direkteingabe fossil_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>Baulich Direkteingabe biogen_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>Baulich 
+Direkteingabe Lebensdauer_Jahre</t>
+  </si>
+  <si>
+    <t>Spalte132_</t>
+  </si>
+  <si>
+    <t>Spalte133_</t>
+  </si>
+  <si>
+    <t>Baulich Direkteingabe_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>Baulich Errichtung_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>Baulich Instandsetzung_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>Baulich Fossil_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>Baulich Biogen_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>Baulich_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>Biogen+Fossil = Errichtung + Instandsetzung_WAHR</t>
+  </si>
+  <si>
+    <t>Spalte134_</t>
+  </si>
+  <si>
+    <t>Komponenten-Lebensdauern sind positiv_WAHR</t>
+  </si>
+  <si>
+    <t>TGA PV fossil_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>TGA PV biogen_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>TGA PV Lebensdauer_Jahre</t>
+  </si>
+  <si>
+    <t>TGA PV_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>TGA Erdsonden fossil_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>TGA Erdsonden biogen_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>TGA Erdsonden Lebensdauer_Jahre</t>
+  </si>
+  <si>
+    <t>TGA Erdsonden_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>TGA Lüftung fossil_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>TGA Lüftung biogen_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>TGA Lüftung Lebensdauer_Jahre</t>
+  </si>
+  <si>
+    <t>TGA Lüftung_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>TGA Solarthermie fossil_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>TGA Solarthermie biogen_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>TGA Solarthermie Lebensdauer_Jahre</t>
+  </si>
+  <si>
+    <t>TGA Solarthermie_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>TGA E-Batterie fossil_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>TGA E-Batterie biogen_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>TGA E-Batterie Lebensdauer_Jahre</t>
+  </si>
+  <si>
+    <t>TGA E-Batterie_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>TGA Speicher fossil_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>TGA Speicher biogen_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>TGA Speicher Lebensdauer_Jahre</t>
+  </si>
+  <si>
+    <t>TGA Speicher_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>TGA Allgemein fossil_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>TGA Allgemein biogen_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>TGA Allgemein Lebensdauer_Jahre</t>
+  </si>
+  <si>
+    <t>TGA Allgemein_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>TGA Andere fossil_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>TGA Andere biogen_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>TGA Andere Lebensdauer_Jahre</t>
+  </si>
+  <si>
+    <t>TGA Sammel-Maßnahmen_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>Errichtung TGA_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>Instandsetzung TGA_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>TGA_GWP 100A (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>Spalte135_</t>
+  </si>
+  <si>
+    <t>Errichtung Mobilität fossil_GWP 100S (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>Errichtung Mobilität Elektrisch_GWP 100S (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>Errichtung Mobilität_GWP 100S (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>Spalte136_</t>
+  </si>
+  <si>
+    <t>Spalte137_</t>
+  </si>
+  <si>
+    <t>Spalte138_</t>
+  </si>
+  <si>
+    <t>Betrieb Gebäude Netzstrombezug_GWP pro Jahr (kgCO2equiv/m²BGFa)</t>
+  </si>
+  <si>
+    <t>Betrieb Gebäude Flexibler Netzbezug_GWP pro Jahr (kgCO2equiv/m²BGFa)</t>
+  </si>
+  <si>
+    <t>Betrieb EV Ladung Insgesamt_GWP pro Jahr (kgCO2equiv/m²BGFa)</t>
+  </si>
+  <si>
+    <t>Spalte139_</t>
+  </si>
+  <si>
+    <t>Spalte140_</t>
+  </si>
+  <si>
+    <t>Betrieb Batterie Beladung_GWP pro Jahr (kgCO2equiv/m²BGFa)</t>
+  </si>
+  <si>
+    <t>Emissions-Intensität Netzstrom allgemein_gCO2eq/kWh</t>
+  </si>
+  <si>
+    <t>Emissions-Intensität Netzstrombezug_gCO2eq/kWh</t>
+  </si>
+  <si>
+    <t>Emissions-Intensität Flexibler Netzbezug_gCO2eq/kWh</t>
+  </si>
+  <si>
+    <t>Emissions-Intensität Batterie Beladung_gCO2eq/kWh</t>
+  </si>
+  <si>
+    <t>Emissions-Intensität EV ladung_gCO2eq/kWh</t>
+  </si>
+  <si>
+    <t>Emissions-Intensität Netzeinspeisung_gCO2eq/kWh</t>
+  </si>
+  <si>
+    <t>Spalte141_</t>
+  </si>
+  <si>
+    <t>Betrieb Nutzerstrom GEHT SO NICHT_GWP pro Jahr (kgCO2equiv/m²BGFa)</t>
+  </si>
+  <si>
+    <t>Betrieb HKLS elektrisch NEU_GWP pro Jahr (kgCO2equiv/m²BGFa)</t>
+  </si>
+  <si>
+    <t>Betrieb Gebäude Netzstrombezug142_GWP pro Jahr (kgCO2equiv/m²BGFa)</t>
+  </si>
+  <si>
+    <t>Betrieb Gebäude Flexibler Netzbezug143_GWP pro Jahr (kgCO2equiv/m²BGFa)</t>
+  </si>
+  <si>
+    <t>Betrieb HKLS Fernwärme_GWP pro Jahr (kgCO2equiv/m²BGFa)</t>
+  </si>
+  <si>
+    <t>Betrieb HKLS Erdgas_GWP pro Jahr (kgCO2equiv/m²BGFa)</t>
+  </si>
+  <si>
+    <t>Betrieb HKLS Biomasse_GWP pro Jahr (kgCO2equiv/m²BGFa)</t>
+  </si>
+  <si>
+    <t>Betrieb HKLS Sonstige_GWP pro Jahr (kgCO2equiv/m²BGFa)</t>
+  </si>
+  <si>
+    <t>Betrieb Netzeinspeisung_GWP pro Jahr (kgCO2equiv/m²BGFa)</t>
+  </si>
+  <si>
+    <t>Betrieb Gebäude_GWP pro Jahr (kgCO2equiv/m²BGFa)</t>
+  </si>
+  <si>
+    <t>Spalte144_</t>
+  </si>
+  <si>
+    <t>Spalte145_</t>
+  </si>
+  <si>
+    <t>GWP MIV elektrisch INSGESAMTE LADUNG_GWP pro Jahr (kgCO2equiv/m²BGFa)</t>
+  </si>
+  <si>
+    <t>GWP MIV Export (Anderer Verkehr)_GWP pro Jahr (kgCO2equiv/m²BGFa)</t>
+  </si>
+  <si>
+    <t>GWP MIV fossil_GWP pro Jahr (kgCO2equiv/m²BGFa)</t>
+  </si>
+  <si>
+    <t>Mobilität (Ursächlich)_GWP pro Jahr (kgCO2equiv/m²BGFa)</t>
+  </si>
+  <si>
+    <t>Spalte146_</t>
+  </si>
+  <si>
+    <t>GWP Quartier (Gebäude+MIV)_GWP pro Jahr (kgCO2equiv/m²BGFa)</t>
+  </si>
+  <si>
+    <t>Spalte147_</t>
+  </si>
+  <si>
+    <t>LZ Betrieb Gebäude Netzstrombezug_GWP 100S (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>LZ Betrieb Gebäude Flexibler Netzbezug_GWP 100S (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>LZ Betrieb HKLS Fernwärme_GWP 100S (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>LZ Betrieb HKLS Erdgas_GWP 100S (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>LZ Betrieb HKLS Biomasse_GWP 100S (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>LZ Betrieb HKLS Sonstige_GWP 100S (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>LZ Betrieb Netzeinspeisung_GWP 100S (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>LZ Betrieb Gebäude_</t>
+  </si>
+  <si>
+    <t>LZ Betrieb Gebäude Emissionen_</t>
+  </si>
+  <si>
+    <t>LZ Betrieb Gebäude Vermiedene Emissionen_</t>
+  </si>
+  <si>
+    <t>LCA OE MIV elektrisch_GWP 100S (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>LV Mobilitäts-Export_GWP 100S (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>LCA OE MIV fossil_GWP 100S (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>Mobilität_GWP 100S (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>Spalte148_</t>
+  </si>
+  <si>
+    <t>THG-Emissionen 2025-2075_GWP 100S (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>OE THG-Emissionen 2025-2075_GWP 100S (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>EE THG-Emissionen 2025-2075_GWP 100S (kgCO2equiv/m²BGF)</t>
+  </si>
+  <si>
+    <t>OE + EE = LCA_WAHR</t>
+  </si>
+  <si>
+    <t>Kosten Netzbezug_€</t>
+  </si>
+  <si>
+    <t>Kosten Flexibler Bezug_€</t>
+  </si>
+  <si>
+    <t>Kosten Netzeinspeisung_€</t>
+  </si>
+  <si>
+    <t>Summe Kosten_€</t>
+  </si>
+  <si>
+    <t>Kosten Netzbezug Durchschnitt_€/kWh</t>
+  </si>
+  <si>
+    <t>Kosten Flexibler Bezug Durchschnitt_€/kWh</t>
+  </si>
+  <si>
+    <t>Kosten Netzeinspeisung Durchschnitt_€/kWh</t>
+  </si>
+  <si>
+    <t>Spalte149_</t>
+  </si>
+  <si>
+    <t>Freigabesignal Anteil Jahr_</t>
+  </si>
+  <si>
+    <t>Freigabesignal Anteil  Winter_</t>
+  </si>
+  <si>
+    <t>Freigabesignal Anteil  Sommer_</t>
+  </si>
+  <si>
+    <t>Flex GSRU_</t>
+  </si>
+  <si>
+    <t>Flex GSRI_</t>
+  </si>
+  <si>
+    <t>Flex GSR_</t>
+  </si>
+  <si>
+    <t>PV Eigenverbrauch direkt_</t>
+  </si>
+  <si>
+    <t>PV Eigenverbrauch flex_</t>
+  </si>
+  <si>
+    <t>PV Eigenverbrauch insgesamt_</t>
+  </si>
+  <si>
+    <t>Energie-Autonomie_</t>
+  </si>
+  <si>
+    <t>Spalte150_</t>
+  </si>
+  <si>
+    <t>Spalte151_</t>
+  </si>
+  <si>
+    <t>Batterie in Verwendung_bool</t>
+  </si>
+  <si>
+    <t>Batterie Jährliche Beladung_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Jährliche Entladung_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Verluste Beladung_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Verluste Entladung_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Round-Trip- Efficiency_</t>
+  </si>
+  <si>
+    <t>Batterie Volladezyklen_x</t>
+  </si>
+  <si>
+    <t>Spalte152_</t>
+  </si>
+  <si>
+    <t>Spalte153_</t>
+  </si>
+  <si>
+    <t>Wohnbau_StatPAX</t>
+  </si>
+  <si>
+    <t>Arbeit_StatPAX</t>
+  </si>
+  <si>
+    <t>Büro und Gewerbe_StatPAX</t>
+  </si>
+  <si>
+    <t>Bildundseinrichtungen (Kindergarten, Primär)_StatPAX</t>
+  </si>
+  <si>
+    <t>Bildungseinrichtung (sekundär, Tertiär)_StatPAX</t>
+  </si>
+  <si>
+    <t>Einkaufen_StatPAX</t>
+  </si>
+  <si>
+    <t>Lebensmittelhandel (Supermarkt)_StatPAX</t>
+  </si>
+  <si>
+    <t>Handel Sonstige_StatPAX</t>
+  </si>
+  <si>
+    <t>Quartier153_StatPAX</t>
+  </si>
+  <si>
+    <t>Wohnen_km/a</t>
+  </si>
+  <si>
+    <t>Arbeit154_km/a</t>
+  </si>
+  <si>
+    <t>Bildungseinrichtung (sekundär, Tertiär)155_km/a</t>
+  </si>
+  <si>
+    <t>Handel_km/a</t>
+  </si>
+  <si>
+    <t>Gesamtverkehr_km/a</t>
+  </si>
+  <si>
+    <t>Gesamtverkehr pro STATPAX_km/PAX/a</t>
+  </si>
+  <si>
+    <t>Zielverkehr zum Quartier_km/a</t>
+  </si>
+  <si>
+    <t>Zielverkehr Elektrisch_km/a</t>
+  </si>
+  <si>
+    <t>Zielverkehr Fossil_km/a</t>
+  </si>
+  <si>
+    <t>Zielverkehr zum Quartier pro Person_km/PAX/a</t>
+  </si>
+  <si>
+    <t>Zielverkehrsanteil_</t>
+  </si>
+  <si>
+    <t>Spalte156_</t>
+  </si>
+  <si>
+    <t>Quell- und anderer Verkehr_km/a</t>
+  </si>
+  <si>
+    <t>Alle Wege_km/a</t>
+  </si>
+  <si>
+    <t>EE-Bedarf Zielverkehr Elektrisch_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>EE-Bedarf Zielverkehr Fossil_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Spalte157_</t>
+  </si>
+  <si>
+    <t>Anzahl E-Cars_</t>
+  </si>
+  <si>
+    <t>Batterie-Kapazität_Wh/m²</t>
+  </si>
+  <si>
+    <t>EV Volladezyklen_</t>
+  </si>
+  <si>
+    <t>Gesamtverkehr elektrisch_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Quell- und anderer Verkehr elektrisch_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Spalte158_</t>
+  </si>
+  <si>
+    <t>EV Jährliche Beladung_</t>
+  </si>
+  <si>
+    <t>EV Jährliche Entladung_</t>
+  </si>
+  <si>
+    <t>EV Verluste_</t>
+  </si>
+  <si>
+    <t>EV Verluste Beladung_</t>
+  </si>
+  <si>
+    <t>Spalte4_</t>
+  </si>
+  <si>
+    <t>Hilfssstrom Heizen_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Hilfsstrom Kühlen_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Hilfsstrom Warmwasser_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Spalte5_</t>
+  </si>
+  <si>
+    <t>WW-Wärmebedarf_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>WW Endenergiebedarf Thermisch_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>WW Endenergiebedarf Elektrisch (inkl. Hilfsstrom)_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>WW Hilfsstrom_</t>
+  </si>
+  <si>
+    <t>WW 1 Endenergie thermisch_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>WW 1 Endenergie elektrisch (inkl. Hilfsstrom)_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>WW 1 Hilfsstrom_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>WW 2 Endenergie thermisch_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>WW 2 Endenergie elektrisch (inkl.Hilfsstrom)_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>WW 2 Hilfsstrom_kWh/m²NGFa</t>
+  </si>
+  <si>
+    <t>Column name in "Model_BuildingSector.xlsb"!💾building_energy_data</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Total Net floor Area</t>
+  </si>
+  <si>
+    <t>m²NFA</t>
+  </si>
+  <si>
+    <t>Domain Variable</t>
+  </si>
+  <si>
+    <t>NFA</t>
+  </si>
+  <si>
+    <t>Example Constraint</t>
+  </si>
+  <si>
+    <t>i</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>kWh/m²NFA</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>HWB</t>
+  </si>
+  <si>
+    <t>Grid</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,16 +1628,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor theme="7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -45,15 +1659,61 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="7" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="7" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="7" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="7" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="7" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="7" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="7" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="7" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -66,6 +1726,491 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>20320</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1469698" cy="475515"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2" name="Textfeld 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{72A40E3B-EC09-5E6E-F81F-A17D966C73AE}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6841490" y="386080"/>
+              <a:ext cx="1469698" cy="475515"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:nary>
+                      <m:naryPr>
+                        <m:chr m:val="∑"/>
+                        <m:ctrlPr>
+                          <a:rPr lang="de-DE" sz="1100" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:naryPr>
+                      <m:sub>
+                        <m:r>
+                          <m:rPr>
+                            <m:brk m:alnAt="23"/>
+                          </m:rPr>
+                          <a:rPr lang="de-DE" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="de-DE" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>=1</m:t>
+                        </m:r>
+                      </m:sub>
+                      <m:sup>
+                        <m:r>
+                          <a:rPr lang="de-DE" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>1441</m:t>
+                        </m:r>
+                      </m:sup>
+                      <m:e>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="de-DE" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="de-DE" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑥</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="de-DE" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑖</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                        <m:r>
+                          <a:rPr lang="de-DE" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>=878 </m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="de-DE" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑚𝑖𝑜</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="de-DE" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t> </m:t>
+                        </m:r>
+                        <m:sSubSup>
+                          <m:sSubSupPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="de-DE" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubSupPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="de-DE" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑚</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="de-DE" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑁𝐹𝐴</m:t>
+                            </m:r>
+                          </m:sub>
+                          <m:sup>
+                            <m:r>
+                              <a:rPr lang="de-DE" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>2</m:t>
+                            </m:r>
+                          </m:sup>
+                        </m:sSubSup>
+                      </m:e>
+                    </m:nary>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="de-DE" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2" name="Textfeld 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{72A40E3B-EC09-5E6E-F81F-A17D966C73AE}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6841490" y="386080"/>
+              <a:ext cx="1469698" cy="475515"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="de-DE" sz="1100" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>∑24_(</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="de-DE" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑖=1)^1441▒〖𝑥_𝑖=878 𝑚𝑖𝑜 𝑚_𝑁𝐹𝐴^2 〗</a:t>
+              </a:r>
+              <a:endParaRPr lang="de-DE" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>117282</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>31087</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1764201" cy="474617"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3" name="Textfeld 2">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0324B640-6AEB-415A-BFD5-9082F48503B6}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="8446273" y="402148"/>
+              <a:ext cx="1764201" cy="474617"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:nary>
+                      <m:naryPr>
+                        <m:chr m:val="∑"/>
+                        <m:ctrlPr>
+                          <a:rPr lang="de-DE" sz="1100" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:naryPr>
+                      <m:sub>
+                        <m:r>
+                          <m:rPr>
+                            <m:brk m:alnAt="23"/>
+                          </m:rPr>
+                          <a:rPr lang="de-DE" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝐼𝐷</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="de-DE" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>=1</m:t>
+                        </m:r>
+                      </m:sub>
+                      <m:sup>
+                        <m:r>
+                          <a:rPr lang="de-DE" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>1441</m:t>
+                        </m:r>
+                      </m:sup>
+                      <m:e>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="de-DE" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="de-DE" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑁𝐹𝐴</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="de-DE" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝐼𝐷</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                        <m:r>
+                          <a:rPr lang="de-DE" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>=878 </m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="de-DE" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑚𝑖𝑜</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="de-DE" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t> </m:t>
+                        </m:r>
+                        <m:sSubSup>
+                          <m:sSubSupPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="de-DE" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubSupPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="de-DE" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑚</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="de-DE" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑁𝐹𝐴</m:t>
+                            </m:r>
+                          </m:sub>
+                          <m:sup>
+                            <m:r>
+                              <a:rPr lang="de-DE" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>2</m:t>
+                            </m:r>
+                          </m:sup>
+                        </m:sSubSup>
+                      </m:e>
+                    </m:nary>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="de-DE" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3" name="Textfeld 2">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0324B640-6AEB-415A-BFD5-9082F48503B6}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="8446273" y="402148"/>
+              <a:ext cx="1764201" cy="474617"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="de-DE" sz="1100" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>∑24_(</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="de-DE" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝐼𝐷=1)^1441▒〖〖𝑁𝐹𝐴〗_𝐼𝐷=878 𝑚𝑖𝑜 𝑚_𝑁𝐹𝐴^2 〗</a:t>
+              </a:r>
+              <a:endParaRPr lang="de-DE" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -330,10 +2475,2624 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E514"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="10.453125" customWidth="1"/>
+    <col min="4" max="4" width="62.1796875" customWidth="1"/>
+    <col min="5" max="5" width="23.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B1" t="s">
+        <v>516</v>
+      </c>
+      <c r="C1" t="s">
+        <v>513</v>
+      </c>
+      <c r="D1" t="s">
+        <v>511</v>
+      </c>
+      <c r="E1" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>519</v>
+      </c>
+      <c r="B2" t="s">
+        <v>512</v>
+      </c>
+      <c r="D2" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B3" t="s">
+        <v>517</v>
+      </c>
+      <c r="C3" t="s">
+        <v>515</v>
+      </c>
+      <c r="D3" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="D4" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="D5" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="D6" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="D7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="D8" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="D9" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="D10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="D11" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="D12" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="D13" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="D14" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="D15" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="D16" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+      <c r="D17" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+      <c r="D18" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+      <c r="D19" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+      <c r="D20" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+      <c r="D21" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+      <c r="D22" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+      <c r="D23" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D24" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D25" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D26" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>522</v>
+      </c>
+      <c r="B27" t="s">
+        <v>523</v>
+      </c>
+      <c r="C27" t="s">
+        <v>521</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D28" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D29" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D30" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D31" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D32" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D33" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D34" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D35" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D36" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="37" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D37" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D38" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="39" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D39" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="40" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D40" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="41" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D41" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="42" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D42" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="43" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D43" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="44" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D44" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="45" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D45" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="46" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D46" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="47" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D47" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="48" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D48" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="49" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D49" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="50" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D50" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="51" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D51" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="52" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D52" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="53" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D53" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="54" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D54" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="55" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D55" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="56" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D56" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="57" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D57" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="58" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D58" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="59" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D59" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="60" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D60" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="61" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D61" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="62" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D62" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="63" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D63" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="64" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D64" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="65" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D65" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="66" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D66" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="67" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D67" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="68" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D68" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="69" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D69" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="70" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D70" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="71" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D71" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="72" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D72" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="73" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D73" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="74" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D74" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="75" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D75" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="76" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D76" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="77" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D77" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="78" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D78" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="79" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D79" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="80" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D80" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="81" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D81" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="82" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D82" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="83" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D83" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="84" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D84" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="85" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D85" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="86" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D86" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="87" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D87" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="88" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D88" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="89" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D89" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="90" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D90" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="91" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D91" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="92" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D92" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="93" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D93" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="94" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D94" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="95" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D95" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="96" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D96" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="97" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D97" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="98" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D98" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="99" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D99" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="100" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D100" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="101" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D101" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="102" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D102" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="103" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D103" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="104" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D104" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="105" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D105" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="106" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D106" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="107" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D107" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="108" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D108" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="109" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D109" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="110" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D110" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="111" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D111" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="112" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D112" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="113" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D113" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="114" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D114" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="115" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D115" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="116" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D116" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="117" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D117" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="118" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D118" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="119" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D119" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="120" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D120" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="121" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D121" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="122" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D122" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="123" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D123" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="124" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D124" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="125" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D125" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="126" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D126" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="127" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D127" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="128" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D128" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="129" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D129" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="130" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D130" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="131" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D131" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="132" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D132" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="133" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D133" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="134" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D134" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="135" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D135" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="136" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D136" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="137" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D137" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="138" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D138" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="139" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D139" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="140" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D140" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="141" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D141" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="142" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D142" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="143" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D143" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="144" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D144" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="145" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D145" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="146" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D146" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="147" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D147" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="148" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D148" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="149" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D149" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="150" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D150" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="151" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D151" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="152" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D152" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="153" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D153" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="154" spans="4:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="D154" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="155" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D155" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="156" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D156" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="157" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D157" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="158" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D158" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="159" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D159" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="160" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D160" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="161" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D161" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="162" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D162" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="163" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D163" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="164" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D164" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="165" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D165" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="166" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D166" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="167" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D167" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="168" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D168" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="169" spans="4:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="D169" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="170" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D170" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="171" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D171" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="172" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D172" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="173" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D173" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="174" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D174" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="175" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D175" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="176" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D176" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="177" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D177" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="178" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D178" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="179" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D179" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="180" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D180" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="181" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D181" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="182" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D182" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="183" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D183" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="184" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D184" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="185" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D185" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="186" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D186" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="187" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D187" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="188" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D188" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="189" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D189" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="190" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D190" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="191" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D191" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="192" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D192" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="193" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D193" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="194" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D194" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="195" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D195" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="196" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D196" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="197" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D197" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="198" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D198" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="199" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D199" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="200" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D200" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="201" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D201" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="202" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D202" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="203" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D203" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="204" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D204" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="205" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D205" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="206" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D206" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="207" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D207" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="208" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D208" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="209" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D209" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="210" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D210" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="211" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D211" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="212" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D212" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="213" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B213" t="s">
+        <v>524</v>
+      </c>
+      <c r="D213" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="214" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D214" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="215" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D215" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="216" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D216" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="217" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D217" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="218" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D218" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="219" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D219" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="220" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D220" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="221" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D221" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="222" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D222" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="223" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D223" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="224" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D224" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="225" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D225" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="226" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D226" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="227" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D227" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="228" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D228" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="229" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D229" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="230" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D230" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="231" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D231" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="232" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D232" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="233" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D233" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="234" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D234" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="235" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D235" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="236" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D236" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="237" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D237" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="238" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D238" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="239" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D239" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="240" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D240" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="241" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D241" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="242" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D242" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="243" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D243" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="244" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D244" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="245" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D245" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="246" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D246" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="247" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D247" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="248" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D248" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="249" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D249" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="250" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D250" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="251" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D251" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="252" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D252" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="253" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D253" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="254" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D254" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="255" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D255" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="256" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D256" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="257" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D257" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="258" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D258" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="259" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D259" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="260" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D260" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="261" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D261" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="262" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D262" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="263" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D263" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="264" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D264" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="265" spans="4:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="D265" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="266" spans="4:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="D266" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="267" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D267" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="268" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D268" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="269" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D269" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="270" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D270" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="271" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D271" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="272" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D272" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="273" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D273" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="274" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D274" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="275" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D275" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="276" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D276" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="277" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D277" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="278" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D278" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="279" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D279" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="280" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D280" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="281" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D281" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="282" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D282" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="283" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D283" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="284" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D284" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="285" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D285" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="286" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D286" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="287" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D287" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="288" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D288" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="289" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D289" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="290" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D290" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="291" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D291" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="292" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D292" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="293" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D293" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="294" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D294" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="295" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D295" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="296" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D296" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="297" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D297" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="298" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D298" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="299" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D299" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="300" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D300" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="301" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D301" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="302" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D302" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="303" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D303" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="304" spans="4:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="D304" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="305" spans="4:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="D305" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="306" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D306" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="307" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D307" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="308" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D308" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="309" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D309" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="310" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D310" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="311" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D311" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="312" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D312" s="2" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="313" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D313" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="314" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D314" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="315" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D315" s="2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="316" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D316" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="317" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D317" s="2" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="318" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D318" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="319" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D319" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="320" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D320" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="321" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D321" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="322" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D322" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="323" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D323" s="2" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="324" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D324" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="325" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D325" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="326" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D326" s="2" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="327" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D327" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="328" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D328" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="329" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D329" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="330" spans="4:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="D330" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="331" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D331" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="332" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D332" s="2" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="333" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D333" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="334" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D334" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="335" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D335" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="336" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D336" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="337" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D337" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="338" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D338" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="339" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D339" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="340" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D340" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="341" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D341" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="342" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D342" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="343" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D343" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="344" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D344" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="345" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D345" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="346" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D346" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="347" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D347" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="348" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D348" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="349" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D349" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="350" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D350" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="351" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D351" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="352" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D352" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="353" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D353" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="354" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D354" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="355" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D355" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="356" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D356" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="357" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D357" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="358" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D358" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="359" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D359" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="360" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D360" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="361" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D361" s="2" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="362" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D362" s="2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="363" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D363" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="364" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D364" s="2" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="365" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D365" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="366" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D366" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="367" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D367" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="368" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D368" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="369" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D369" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="370" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D370" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="371" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D371" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="372" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D372" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="373" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D373" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="374" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D374" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="375" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D375" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="376" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D376" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="377" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D377" s="2" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="378" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D378" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="379" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D379" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="380" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D380" s="2" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="381" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D381" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="382" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D382" s="2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="383" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D383" s="2" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="384" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D384" s="2" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="385" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D385" s="2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="386" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D386" s="2" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="387" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D387" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="388" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D388" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="389" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D389" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="390" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D390" s="2" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="391" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D391" s="2" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="392" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D392" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="393" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D393" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="394" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D394" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="395" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D395" s="2" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="396" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D396" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="397" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D397" s="2" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="398" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D398" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="399" spans="4:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="D399" s="2" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="400" spans="4:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="D400" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="401" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D401" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="402" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D402" s="2" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="403" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D403" s="2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="404" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D404" s="2" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="405" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D405" s="2" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="406" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D406" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="407" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D407" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="408" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D408" s="2" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="409" spans="4:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="D409" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="410" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D410" s="2" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="411" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D411" s="2" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="412" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D412" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="413" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D413" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="414" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D414" s="2" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="415" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D415" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="416" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D416" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="417" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D417" s="2" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="418" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D418" s="2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="419" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D419" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="420" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D420" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="421" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D421" s="2" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="422" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D422" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="423" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D423" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="424" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D424" s="2" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="425" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D425" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="426" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D426" s="2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="427" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D427" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="428" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D428" s="2" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="429" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D429" s="2" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="430" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D430" s="2" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="431" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D431" s="2" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="432" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D432" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="433" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D433" s="2" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="434" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D434" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="435" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D435" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="436" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D436" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="437" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D437" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="438" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D438" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="439" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D439" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="440" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D440" s="2" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="441" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D441" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="442" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D442" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="443" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D443" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="444" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D444" s="2" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="445" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D445" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="446" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D446" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="447" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D447" s="2" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="448" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D448" s="2" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="449" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D449" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="450" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D450" s="2" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="451" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D451" s="2" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="452" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D452" s="2" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="453" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D453" s="2" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="454" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D454" s="2" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="455" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D455" s="2" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="456" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D456" s="2" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="457" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D457" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="458" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D458" s="2" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="459" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D459" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="460" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D460" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="461" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D461" s="2" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="462" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D462" s="2" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="463" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D463" s="2" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="464" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D464" s="2" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="465" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D465" s="2" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="466" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D466" s="2" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="467" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D467" s="2" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="468" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D468" s="2" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="469" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D469" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="470" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D470" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="471" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D471" s="2" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="472" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D472" s="2" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="473" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D473" s="2" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="474" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D474" s="2" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="475" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D475" s="2" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="476" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D476" s="2" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="477" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D477" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="478" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D478" s="2" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="479" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D479" s="2" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="480" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D480" s="2" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="481" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D481" s="2" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="482" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D482" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="483" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D483" s="2" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="484" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D484" s="2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="485" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D485" s="2" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="486" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D486" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="487" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D487" s="2" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="488" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D488" s="2" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="489" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D489" s="2" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="490" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D490" s="2" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="491" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D491" s="2" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="492" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D492" s="2" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="493" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D493" s="2" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="494" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D494" s="2" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="495" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D495" s="2" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="496" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D496" s="2" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="497" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D497" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="498" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D498" s="2" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="499" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D499" s="2" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="500" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D500" s="2" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="501" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D501" s="2" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="502" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D502" s="2" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="503" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D503" s="2" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="504" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D504" s="2" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="505" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D505" s="2" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="506" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D506" s="2" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="507" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D507" s="2" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="508" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D508" s="2" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="509" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D509" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="510" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D510" s="2" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="511" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D511" s="2" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="512" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D512" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="513" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D513" s="2" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="514" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D514" s="3" t="s">
+        <v>510</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>